--- a/dados_acareacoes_shopee.xlsx
+++ b/dados_acareacoes_shopee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
   <si>
     <t>AWB</t>
   </si>
@@ -25,6 +25,9 @@
     <t>Motorista</t>
   </si>
   <si>
+    <t>Telefone</t>
+  </si>
+  <si>
     <t>Plataforma</t>
   </si>
   <si>
@@ -179,6 +182,45 @@
   </si>
   <si>
     <t>ANA RAQUEL MALAQUIAS RAMOS</t>
+  </si>
+  <si>
+    <t>31992536653</t>
+  </si>
+  <si>
+    <t>31994265948</t>
+  </si>
+  <si>
+    <t>31975014471</t>
+  </si>
+  <si>
+    <t>31986430732</t>
+  </si>
+  <si>
+    <t>31987519804</t>
+  </si>
+  <si>
+    <t>31997899259</t>
+  </si>
+  <si>
+    <t>31993664436</t>
+  </si>
+  <si>
+    <t>31996541319</t>
+  </si>
+  <si>
+    <t>31997507362</t>
+  </si>
+  <si>
+    <t>31983175222</t>
+  </si>
+  <si>
+    <t>31993053829</t>
+  </si>
+  <si>
+    <t>31994571517</t>
+  </si>
+  <si>
+    <t>31971283620</t>
   </si>
   <si>
     <t>Shopee</t>
@@ -513,10 +555,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,285 +571,348 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B21" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C21" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>68</v>
+      </c>
+      <c r="E21" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes_shopee.xlsx
+++ b/dados_acareacoes_shopee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>AWB</t>
   </si>
@@ -31,6 +31,15 @@
     <t>Plataforma</t>
   </si>
   <si>
+    <t>BR2607293649391</t>
+  </si>
+  <si>
+    <t>BR266155977408V</t>
+  </si>
+  <si>
+    <t>BR269618276372T</t>
+  </si>
+  <si>
     <t>BR2656724575515</t>
   </si>
   <si>
@@ -40,10 +49,22 @@
     <t>BR2635109064564</t>
   </si>
   <si>
+    <t>BR265369847211X</t>
+  </si>
+  <si>
     <t>BR2678692184486</t>
   </si>
   <si>
-    <t>BR268516064207V</t>
+    <t>BR2644161383330</t>
+  </si>
+  <si>
+    <t>BR266936861820A</t>
+  </si>
+  <si>
+    <t>BR264763341634G</t>
+  </si>
+  <si>
+    <t>BR2689286238103</t>
   </si>
   <si>
     <t>BR265210470152K</t>
@@ -52,6 +73,12 @@
     <t>BR269093691899D</t>
   </si>
   <si>
+    <t>BR268510449338A</t>
+  </si>
+  <si>
+    <t>BR265083035717G</t>
+  </si>
+  <si>
     <t>BR263306332419N</t>
   </si>
   <si>
@@ -61,36 +88,30 @@
     <t>BR266827618645T</t>
   </si>
   <si>
-    <t>BR268344685790Y</t>
-  </si>
-  <si>
-    <t>BR269213422645L</t>
-  </si>
-  <si>
-    <t>BR266929768846E</t>
-  </si>
-  <si>
     <t>BR2641677974682</t>
   </si>
   <si>
     <t>BR266512239937K</t>
   </si>
   <si>
-    <t>BR266000540823Z</t>
-  </si>
-  <si>
     <t>BR261752666850Z</t>
   </si>
   <si>
-    <t>BR269113905373H</t>
-  </si>
-  <si>
     <t>BR269454940769Q</t>
   </si>
   <si>
     <t>BR267650731853B</t>
   </si>
   <si>
+    <t>Eliane Damásia Do Carmo Silva_</t>
+  </si>
+  <si>
+    <t>Vítor Assis Morais Magalhães_</t>
+  </si>
+  <si>
+    <t>Ana Kathlyn Perdigão_</t>
+  </si>
+  <si>
     <t>Fernanda Novais_</t>
   </si>
   <si>
@@ -100,7 +121,19 @@
     <t>Gildeir Gonçalves Da Silva_</t>
   </si>
   <si>
-    <t>Juliana Aquino_</t>
+    <t>Alessandra_</t>
+  </si>
+  <si>
+    <t>Maria Eduarda Ferreira Lima_</t>
+  </si>
+  <si>
+    <t>Alessandra Cassia Alcântara Da Conceição_</t>
+  </si>
+  <si>
+    <t>Barbara Bezerra Soares_</t>
+  </si>
+  <si>
+    <t>Bruna Giardine Araujo_</t>
   </si>
   <si>
     <t>Cassia De Lourdes Machado Carlos_</t>
@@ -109,6 +142,12 @@
     <t>Clede Suellen Barros Da Silva_</t>
   </si>
   <si>
+    <t>Ilma Cicera de Assis_</t>
+  </si>
+  <si>
+    <t>Cláudio José Braga Siqueira_</t>
+  </si>
+  <si>
     <t>Taylane Maria Alcantara Fernandes_</t>
   </si>
   <si>
@@ -118,33 +157,30 @@
     <t>Augusto Cesar Rodrigues Matos_</t>
   </si>
   <si>
-    <t>Ana Clara Pereira Rocha_</t>
-  </si>
-  <si>
-    <t>heloisa campos cordeiro_</t>
-  </si>
-  <si>
     <t>Adriana Aparecida Vitalino_</t>
   </si>
   <si>
     <t>Iasmin Azevedo_</t>
   </si>
   <si>
-    <t>JEFERSON COSME DE SA_</t>
-  </si>
-  <si>
     <t>Marco lima_</t>
   </si>
   <si>
-    <t>Ewerton Assis Patrocínio_</t>
-  </si>
-  <si>
     <t>HAUDINEY FRANKLIN MALAQUIAS_</t>
   </si>
   <si>
     <t>ROMARIO EDISON PINTO CORDEIRO_</t>
   </si>
   <si>
+    <t>KELVE ALEXANDRE FERREIRA  DE CARVALHO</t>
+  </si>
+  <si>
+    <t>TIAGO MOREIRA SANTOS</t>
+  </si>
+  <si>
+    <t>MARCELO DOS SANTOS SOARES</t>
+  </si>
+  <si>
     <t>Giovanni de Souza</t>
   </si>
   <si>
@@ -154,15 +190,27 @@
     <t>GABRIEL JUNIOR ATANAZIO DE ALMEIDA</t>
   </si>
   <si>
-    <t>MARCOS AURÉLIO BRAGA JUNIOR</t>
-  </si>
-  <si>
-    <t>TIAGO MOREIRA SANTOS</t>
+    <t>Messias Cota</t>
+  </si>
+  <si>
+    <t>RAFAEL MOREIRA DOS SANTOS</t>
   </si>
   <si>
     <t>ALINE CRISTINA SANTOS</t>
   </si>
   <si>
+    <t>CARLOS VINICIOS EFIRMIANDO</t>
+  </si>
+  <si>
+    <t>JOAO PAULO BICALHO MARTINS</t>
+  </si>
+  <si>
+    <t>IVAN NELIS XAVIER</t>
+  </si>
+  <si>
+    <t>ANA RAQUEL MALAQUIAS RAMOS</t>
+  </si>
+  <si>
     <t>MARLON NILSON DE SOUZA</t>
   </si>
   <si>
@@ -172,55 +220,73 @@
     <t>BRUNO FELIPE MALAQUIAS RAMOS</t>
   </si>
   <si>
-    <t>AUGUSTO LINO FERREIRA</t>
-  </si>
-  <si>
     <t>RANDLER JUNIOR PINHEIRO ARAUJO</t>
   </si>
   <si>
-    <t>Messias Cota</t>
-  </si>
-  <si>
-    <t>ANA RAQUEL MALAQUIAS RAMOS</t>
-  </si>
-  <si>
-    <t>31992536653</t>
-  </si>
-  <si>
-    <t>31994265948</t>
-  </si>
-  <si>
-    <t>31975014471</t>
-  </si>
-  <si>
-    <t>31986430732</t>
-  </si>
-  <si>
-    <t>31987519804</t>
-  </si>
-  <si>
-    <t>31997899259</t>
-  </si>
-  <si>
-    <t>31993664436</t>
-  </si>
-  <si>
-    <t>31996541319</t>
-  </si>
-  <si>
-    <t>31997507362</t>
-  </si>
-  <si>
-    <t>31983175222</t>
-  </si>
-  <si>
-    <t>31993053829</t>
-  </si>
-  <si>
-    <t>31994571517</t>
-  </si>
-  <si>
-    <t>31971283620</t>
+    <t>5531972398788</t>
+  </si>
+  <si>
+    <t>5531991588483</t>
+  </si>
+  <si>
+    <t>5531971649387</t>
+  </si>
+  <si>
+    <t>5531998983621</t>
+  </si>
+  <si>
+    <t>5531982452481</t>
+  </si>
+  <si>
+    <t>5531972610616</t>
+  </si>
+  <si>
+    <t>5531989827588</t>
+  </si>
+  <si>
+    <t>5531971519875</t>
+  </si>
+  <si>
+    <t>5531999236774</t>
+  </si>
+  <si>
+    <t>5531972116739</t>
+  </si>
+  <si>
+    <t>5531993832638</t>
+  </si>
+  <si>
+    <t>5531997815044</t>
+  </si>
+  <si>
+    <t>5531971410111</t>
+  </si>
+  <si>
+    <t>5531998832100</t>
+  </si>
+  <si>
+    <t>5531996215397</t>
+  </si>
+  <si>
+    <t>5531993021960</t>
+  </si>
+  <si>
+    <t>5531995565833</t>
+  </si>
+  <si>
+    <t>5531997598267</t>
+  </si>
+  <si>
+    <t>5531993365303</t>
+  </si>
+  <si>
+    <t>5531991025387</t>
+  </si>
+  <si>
+    <t>5531999846810</t>
+  </si>
+  <si>
+    <t>5531995706586</t>
   </si>
   <si>
     <t>Shopee</t>
@@ -555,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -580,16 +646,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -597,16 +663,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -614,16 +680,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -631,16 +697,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -648,16 +714,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -665,16 +731,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -682,16 +748,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -699,16 +765,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -716,16 +782,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -733,16 +799,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -750,16 +816,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -767,16 +833,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -784,16 +850,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -801,16 +867,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -818,16 +884,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -835,16 +901,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -852,16 +918,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -869,16 +935,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="E19" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -886,16 +952,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -903,16 +966,84 @@
         <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s">
         <v>68</v>
       </c>
-      <c r="E21" t="s">
-        <v>69</v>
+      <c r="D22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes_shopee.xlsx
+++ b/dados_acareacoes_shopee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
   <si>
     <t>AWB</t>
   </si>
@@ -31,33 +31,21 @@
     <t>Plataforma</t>
   </si>
   <si>
-    <t>BR2607293649391</t>
-  </si>
-  <si>
     <t>BR266155977408V</t>
   </si>
   <si>
-    <t>BR269618276372T</t>
-  </si>
-  <si>
     <t>BR2656724575515</t>
   </si>
   <si>
     <t>BR268515129187E</t>
   </si>
   <si>
-    <t>BR2635109064564</t>
-  </si>
-  <si>
     <t>BR265369847211X</t>
   </si>
   <si>
     <t>BR2678692184486</t>
   </si>
   <si>
-    <t>BR2644161383330</t>
-  </si>
-  <si>
     <t>BR266936861820A</t>
   </si>
   <si>
@@ -67,12 +55,6 @@
     <t>BR2689286238103</t>
   </si>
   <si>
-    <t>BR265210470152K</t>
-  </si>
-  <si>
-    <t>BR269093691899D</t>
-  </si>
-  <si>
     <t>BR268510449338A</t>
   </si>
   <si>
@@ -88,6 +70,9 @@
     <t>BR266827618645T</t>
   </si>
   <si>
+    <t>BR269213422645L</t>
+  </si>
+  <si>
     <t>BR2641677974682</t>
   </si>
   <si>
@@ -103,30 +88,18 @@
     <t>BR267650731853B</t>
   </si>
   <si>
-    <t>Eliane Damásia Do Carmo Silva_</t>
-  </si>
-  <si>
     <t>Vítor Assis Morais Magalhães_</t>
   </si>
   <si>
-    <t>Ana Kathlyn Perdigão_</t>
-  </si>
-  <si>
     <t>Fernanda Novais_</t>
   </si>
   <si>
     <t>Mailena Oliveira_</t>
   </si>
   <si>
-    <t>Gildeir Gonçalves Da Silva_</t>
-  </si>
-  <si>
     <t>Alessandra_</t>
   </si>
   <si>
-    <t>Maria Eduarda Ferreira Lima_</t>
-  </si>
-  <si>
     <t>Alessandra Cassia Alcântara Da Conceição_</t>
   </si>
   <si>
@@ -136,12 +109,6 @@
     <t>Bruna Giardine Araujo_</t>
   </si>
   <si>
-    <t>Cassia De Lourdes Machado Carlos_</t>
-  </si>
-  <si>
-    <t>Clede Suellen Barros Da Silva_</t>
-  </si>
-  <si>
     <t>Ilma Cicera de Assis_</t>
   </si>
   <si>
@@ -157,6 +124,9 @@
     <t>Augusto Cesar Rodrigues Matos_</t>
   </si>
   <si>
+    <t>heloisa campos cordeiro_</t>
+  </si>
+  <si>
     <t>Adriana Aparecida Vitalino_</t>
   </si>
   <si>
@@ -172,30 +142,18 @@
     <t>ROMARIO EDISON PINTO CORDEIRO_</t>
   </si>
   <si>
-    <t>KELVE ALEXANDRE FERREIRA  DE CARVALHO</t>
-  </si>
-  <si>
     <t>TIAGO MOREIRA SANTOS</t>
   </si>
   <si>
-    <t>MARCELO DOS SANTOS SOARES</t>
-  </si>
-  <si>
     <t>Giovanni de Souza</t>
   </si>
   <si>
     <t>Whemes Lemos Aparecido Isidorio</t>
   </si>
   <si>
-    <t>GABRIEL JUNIOR ATANAZIO DE ALMEIDA</t>
-  </si>
-  <si>
     <t>Messias Cota</t>
   </si>
   <si>
-    <t>RAFAEL MOREIRA DOS SANTOS</t>
-  </si>
-  <si>
     <t>ALINE CRISTINA SANTOS</t>
   </si>
   <si>
@@ -217,36 +175,27 @@
     <t>BARBARA RAFAELA DOS SANTOS BASTOS</t>
   </si>
   <si>
+    <t>AUGUSTO LINO FERREIRA</t>
+  </si>
+  <si>
     <t>BRUNO FELIPE MALAQUIAS RAMOS</t>
   </si>
   <si>
     <t>RANDLER JUNIOR PINHEIRO ARAUJO</t>
   </si>
   <si>
-    <t>5531972398788</t>
-  </si>
-  <si>
     <t>5531991588483</t>
   </si>
   <si>
-    <t>5531971649387</t>
-  </si>
-  <si>
     <t>5531998983621</t>
   </si>
   <si>
     <t>5531982452481</t>
   </si>
   <si>
-    <t>5531972610616</t>
-  </si>
-  <si>
     <t>5531989827588</t>
   </si>
   <si>
-    <t>5531971519875</t>
-  </si>
-  <si>
     <t>5531999236774</t>
   </si>
   <si>
@@ -256,22 +205,22 @@
     <t>5531993832638</t>
   </si>
   <si>
-    <t>5531997815044</t>
-  </si>
-  <si>
-    <t>5531971410111</t>
-  </si>
-  <si>
     <t>5531998832100</t>
   </si>
   <si>
     <t>5531996215397</t>
   </si>
   <si>
-    <t>5531993021960</t>
+    <t>********</t>
   </si>
   <si>
     <t>5531995565833</t>
+  </si>
+  <si>
+    <t>5598981599998</t>
+  </si>
+  <si>
+    <t>5531971693386</t>
   </si>
   <si>
     <t>5531997598267</t>
@@ -621,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -646,16 +595,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -663,16 +612,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -680,16 +629,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -697,16 +646,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -714,16 +663,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -731,16 +680,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -748,16 +697,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -765,16 +714,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -782,16 +731,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -799,16 +748,16 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -816,16 +765,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -833,16 +782,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -850,16 +799,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -867,16 +816,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -884,16 +833,16 @@
         <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -901,16 +850,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -918,16 +867,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D18" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -935,16 +884,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -952,98 +901,16 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>50</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>90</v>
-      </c>
-      <c r="E25" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/dados_acareacoes_shopee.xlsx
+++ b/dados_acareacoes_shopee.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="82">
   <si>
     <t>AWB</t>
   </si>
@@ -31,12 +31,27 @@
     <t>Plataforma</t>
   </si>
   <si>
+    <t>BR269646125145J</t>
+  </si>
+  <si>
+    <t>BR263249237752R</t>
+  </si>
+  <si>
+    <t>BR2648610316218</t>
+  </si>
+  <si>
     <t>BR266155977408V</t>
   </si>
   <si>
+    <t>BR269880420517N</t>
+  </si>
+  <si>
     <t>BR2656724575515</t>
   </si>
   <si>
+    <t>BR263842435680Z</t>
+  </si>
+  <si>
     <t>BR268515129187E</t>
   </si>
   <si>
@@ -46,24 +61,24 @@
     <t>BR2678692184486</t>
   </si>
   <si>
+    <t>BR266842459663E</t>
+  </si>
+  <si>
     <t>BR266936861820A</t>
   </si>
   <si>
-    <t>BR264763341634G</t>
-  </si>
-  <si>
-    <t>BR2689286238103</t>
-  </si>
-  <si>
-    <t>BR268510449338A</t>
+    <t>BR268491479307P</t>
+  </si>
+  <si>
+    <t>BR263281935594L</t>
+  </si>
+  <si>
+    <t>BR267081030211R</t>
   </si>
   <si>
     <t>BR265083035717G</t>
   </si>
   <si>
-    <t>BR263306332419N</t>
-  </si>
-  <si>
     <t>BR268447963724W</t>
   </si>
   <si>
@@ -73,12 +88,6 @@
     <t>BR269213422645L</t>
   </si>
   <si>
-    <t>BR2641677974682</t>
-  </si>
-  <si>
-    <t>BR266512239937K</t>
-  </si>
-  <si>
     <t>BR261752666850Z</t>
   </si>
   <si>
@@ -88,36 +97,48 @@
     <t>BR267650731853B</t>
   </si>
   <si>
+    <t>Alice Maria Alves_</t>
+  </si>
+  <si>
+    <t>Pollyana Alves_</t>
+  </si>
+  <si>
+    <t>Conceição  Dos Santos_</t>
+  </si>
+  <si>
     <t>Vítor Assis Morais Magalhães_</t>
   </si>
   <si>
+    <t>Maurício César Nogueira Costa_</t>
+  </si>
+  <si>
     <t>Fernanda Novais_</t>
   </si>
   <si>
+    <t>Cynthia Silva_</t>
+  </si>
+  <si>
     <t>Mailena Oliveira_</t>
   </si>
   <si>
     <t>Alessandra_</t>
   </si>
   <si>
+    <t>Juliana Ramos_</t>
+  </si>
+  <si>
     <t>Alessandra Cassia Alcântara Da Conceição_</t>
   </si>
   <si>
-    <t>Barbara Bezerra Soares_</t>
-  </si>
-  <si>
-    <t>Bruna Giardine Araujo_</t>
-  </si>
-  <si>
-    <t>Ilma Cicera de Assis_</t>
+    <t>Jéssica Lane Rocha Silvério_</t>
+  </si>
+  <si>
+    <t>Maurisia de souza castorino_</t>
   </si>
   <si>
     <t>Cláudio José Braga Siqueira_</t>
   </si>
   <si>
-    <t>Taylane Maria Alcantara Fernandes_</t>
-  </si>
-  <si>
     <t>JCCS Santos_</t>
   </si>
   <si>
@@ -127,12 +148,6 @@
     <t>heloisa campos cordeiro_</t>
   </si>
   <si>
-    <t>Adriana Aparecida Vitalino_</t>
-  </si>
-  <si>
-    <t>Iasmin Azevedo_</t>
-  </si>
-  <si>
     <t>Marco lima_</t>
   </si>
   <si>
@@ -142,78 +157,90 @@
     <t>ROMARIO EDISON PINTO CORDEIRO_</t>
   </si>
   <si>
+    <t>MARCOS AURÉLIO BRAGA JUNIOR</t>
+  </si>
+  <si>
+    <t>IVAN NELIS XAVIER</t>
+  </si>
+  <si>
+    <t>ROGER CARLOS BRAGA</t>
+  </si>
+  <si>
     <t>TIAGO MOREIRA SANTOS</t>
   </si>
   <si>
+    <t>JADERSON VINICIUS FAUSTINO BRANDÃO</t>
+  </si>
+  <si>
     <t>Giovanni de Souza</t>
   </si>
   <si>
+    <t>JACINARA DE SOUZA CRUZELINDO</t>
+  </si>
+  <si>
     <t>Whemes Lemos Aparecido Isidorio</t>
   </si>
   <si>
     <t>Messias Cota</t>
   </si>
   <si>
+    <t>BRUNO FELIPE MALAQUIAS RAMOS</t>
+  </si>
+  <si>
     <t>ALINE CRISTINA SANTOS</t>
   </si>
   <si>
-    <t>CARLOS VINICIOS EFIRMIANDO</t>
-  </si>
-  <si>
-    <t>JOAO PAULO BICALHO MARTINS</t>
-  </si>
-  <si>
-    <t>IVAN NELIS XAVIER</t>
-  </si>
-  <si>
     <t>ANA RAQUEL MALAQUIAS RAMOS</t>
   </si>
   <si>
-    <t>MARLON NILSON DE SOUZA</t>
-  </si>
-  <si>
     <t>BARBARA RAFAELA DOS SANTOS BASTOS</t>
   </si>
   <si>
     <t>AUGUSTO LINO FERREIRA</t>
   </si>
   <si>
-    <t>BRUNO FELIPE MALAQUIAS RAMOS</t>
-  </si>
-  <si>
-    <t>RANDLER JUNIOR PINHEIRO ARAUJO</t>
+    <t>5531994493665</t>
+  </si>
+  <si>
+    <t>5531972198768</t>
+  </si>
+  <si>
+    <t>5531997972341</t>
   </si>
   <si>
     <t>5531991588483</t>
   </si>
   <si>
+    <t>5573981620997</t>
+  </si>
+  <si>
     <t>5531998983621</t>
   </si>
   <si>
+    <t>5531999558674</t>
+  </si>
+  <si>
     <t>5531982452481</t>
   </si>
   <si>
     <t>5531989827588</t>
   </si>
   <si>
+    <t>5531972092336</t>
+  </si>
+  <si>
     <t>5531999236774</t>
   </si>
   <si>
-    <t>5531972116739</t>
-  </si>
-  <si>
-    <t>5531993832638</t>
-  </si>
-  <si>
-    <t>5531998832100</t>
+    <t>5531971541573</t>
+  </si>
+  <si>
+    <t>5531987849722</t>
   </si>
   <si>
     <t>5531996215397</t>
   </si>
   <si>
-    <t>********</t>
-  </si>
-  <si>
     <t>5531995565833</t>
   </si>
   <si>
@@ -221,12 +248,6 @@
   </si>
   <si>
     <t>5531971693386</t>
-  </si>
-  <si>
-    <t>5531997598267</t>
-  </si>
-  <si>
-    <t>5531993365303</t>
   </si>
   <si>
     <t>5531991025387</t>
@@ -570,7 +591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -595,16 +616,16 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -612,16 +633,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -629,16 +650,16 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -646,16 +667,16 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -663,16 +684,16 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -680,16 +701,16 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -697,16 +718,16 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -714,16 +735,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -731,16 +752,16 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -751,13 +772,13 @@
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -765,16 +786,16 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -782,16 +803,16 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -799,16 +820,16 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -816,16 +837,16 @@
         <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -836,13 +857,13 @@
         <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -850,16 +871,16 @@
         <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -867,16 +888,16 @@
         <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -884,16 +905,16 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -901,16 +922,67 @@
         <v>23</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
